--- a/Kerki Comp Results 16-30.xlsx
+++ b/Kerki Comp Results 16-30.xlsx
@@ -1382,7 +1382,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>SHOOOOOOP</t>
+          <t>JobW</t>
         </is>
       </c>
       <c r="M5" t="n">
